--- a/series_data/the-drift/series_log.xlsx
+++ b/series_data/the-drift/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -759,6 +759,281 @@
       <c r="M6" t="inlineStr">
         <is>
           <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-drift/episodes/ep01/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-10 16:38</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/fd299a7f4f30b8437f6e4325a5787ee7_1783701502.mp4</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-drift/episodes/ep02/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-10 16:41</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/185536b277e023d76da0e5a23579cd22_1783701678.mp4</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-drift/episodes/ep02/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-10 16:44</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/1e1ce98d58b4fcebb9750410471242f5_1783701825.mp4</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-drift/episodes/ep02/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-10 16:46</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/5bc10dbfe3e30750efa6f1057d2bfae9_1783701983.mp4</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-drift/episodes/ep02/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-10 16:50</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/530dac93d4a11510c6e430f9c932b0e0_1783702183.mp4</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-drift/episodes/ep02/shots/shot_05.mp4</t>
         </is>
       </c>
     </row>

--- a/series_data/the-drift/series_log.xlsx
+++ b/series_data/the-drift/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1037,6 +1037,281 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-11 15:31</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/vw/9e452e60e61d0b9912730adf83c99cbf.mp4</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-drift/episodes/ep03/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-11 15:33</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/84e04142ec20c4bcc006785914db2960_1783784011.mp4</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-drift/episodes/ep03/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-11 15:36</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/3d6853ed12e4721e3768c948c0bac20e_1783784173.mp4</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-drift/episodes/ep03/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-07-11 15:43</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/vw/38edcebba99c45661444fa3b00ca8a37.mp4</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-drift/episodes/ep03/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-07-11 15:46</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/7921909312de2dc88d2a1b1be69807c2_1783784770.mp4</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-drift/episodes/ep03/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/the-drift/series_log.xlsx
+++ b/series_data/the-drift/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1312,6 +1312,281 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07-12 15:37</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/vw/9587d015db24a7fe0063b97d2271276e.mp4</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-drift/episodes/ep04/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-07-12 15:41</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/vw/a2ff8742b3173e0d6739ea7f97f99a97.mp4</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-drift/episodes/ep04/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-07-12 15:44</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/vw/afc90c13b766bc9429d29e33ea512a3a.mp4</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-drift/episodes/ep04/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-07-12 15:48</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/vw/cd59fac88767476a42314378772e1d81.mp4</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-drift/episodes/ep04/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-07-12 15:52</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/vw/07cb8a5b1052e966090343cecccf18f7.mp4</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-drift/episodes/ep04/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/the-drift/series_log.xlsx
+++ b/series_data/the-drift/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1587,6 +1587,281 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-07-13 16:48</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/vw/15fbc081084564efb9cf6abe49ec362f.mp4</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-drift/episodes/ep05/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-07-13 16:54</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>210.0</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/vw/5c46e10d13460b9a5bb5853a20b8bfc3.mp4</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-drift/episodes/ep05/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-07-13 16:58</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/vw/8c11ac728f828d336c2ef0936c65a109.mp4</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-drift/episodes/ep05/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-07-13 17:01</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/7428a464b20cfb9cf5e2846810e00f09_1783962013.mp4</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-drift/episodes/ep05/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-07-13 17:03</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/07fbbf571773109aa087141bd8966ee3_1783962185.mp4</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-drift/episodes/ep05/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
